--- a/Assets/Excel/BuildingUpgradeSO.xlsx
+++ b/Assets/Excel/BuildingUpgradeSO.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Users\User\TeamProject_CheerUpMyHero\Assets\Excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B206658C-12A8-41C7-AF41-8372DA1782EF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D820F46D-946F-49E8-8BC5-2230F8E0D6D6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="780" yWindow="780" windowWidth="21600" windowHeight="11385" xr2:uid="{529EFE37-1A1C-40A3-AFC4-E608165EEB57}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{529EFE37-1A1C-40A3-AFC4-E608165EEB57}"/>
   </bookViews>
   <sheets>
     <sheet name="BuildingUpgrade" sheetId="1" r:id="rId1"/>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="324" uniqueCount="91">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="365" uniqueCount="105">
   <si>
     <t>idNumber</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -343,6 +343,62 @@
   </si>
   <si>
     <t>UnitCoolDown</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>SpritPath</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>BuildingImages/Empty_tile</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>BuildingImages/Farm_1</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>BuildingImages/Farm_3</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>BuildingImages/Farm_2</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>BuildingImages/Lumberyard_1</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>BuildingImages/Lumberyard_2</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>BuildingImages/Lumberyard_3</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>BuildingImages/Mine_1</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>BuildingImages/Mine_2</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>BuildingImages/Mine_3</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>BuildingImages/Barracks_1</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>BuildingImages/Barracks_2</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>BuildingImages/Barracks_3</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -350,7 +406,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="4">
+  <fonts count="5">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -380,6 +436,15 @@
       <name val="Arial Unicode MS"/>
       <family val="2"/>
     </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="맑은 고딕"/>
+      <family val="3"/>
+      <charset val="129"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
   <fills count="2">
     <fill>
@@ -403,7 +468,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -411,6 +476,9 @@
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
@@ -727,10 +795,10 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{51A90E86-42B4-4D3F-9CF6-60D01B3BDC85}">
-  <dimension ref="A1:Z41"/>
+  <dimension ref="A1:AA41"/>
   <sheetFormatPr defaultRowHeight="16.5"/>
   <sheetData>
-    <row r="1" spans="1:26">
+    <row r="1" spans="1:27">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -809,8 +877,11 @@
       <c r="Z1" s="2" t="s">
         <v>89</v>
       </c>
-    </row>
-    <row r="2" spans="1:26">
+      <c r="AA1" s="3" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="2" spans="1:27">
       <c r="A2">
         <v>101</v>
       </c>
@@ -835,8 +906,11 @@
       <c r="Z2" s="1" t="s">
         <v>85</v>
       </c>
-    </row>
-    <row r="3" spans="1:26">
+      <c r="AA2" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="3" spans="1:27">
       <c r="A3">
         <v>102</v>
       </c>
@@ -879,8 +953,11 @@
       <c r="Z3" s="1" t="s">
         <v>85</v>
       </c>
-    </row>
-    <row r="4" spans="1:26">
+      <c r="AA3" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="4" spans="1:27">
       <c r="A4">
         <v>103</v>
       </c>
@@ -923,8 +1000,11 @@
       <c r="Z4" s="1" t="s">
         <v>85</v>
       </c>
-    </row>
-    <row r="5" spans="1:26">
+      <c r="AA4" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="5" spans="1:27">
       <c r="A5">
         <v>104</v>
       </c>
@@ -973,8 +1053,11 @@
       <c r="Z5" s="1" t="s">
         <v>85</v>
       </c>
-    </row>
-    <row r="6" spans="1:26">
+      <c r="AA5" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="6" spans="1:27">
       <c r="A6">
         <v>105</v>
       </c>
@@ -1029,8 +1112,11 @@
       <c r="Z6" s="1" t="s">
         <v>85</v>
       </c>
-    </row>
-    <row r="7" spans="1:26">
+      <c r="AA6" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="7" spans="1:27">
       <c r="A7">
         <v>106</v>
       </c>
@@ -1085,8 +1171,11 @@
       <c r="Z7" s="1" t="s">
         <v>85</v>
       </c>
-    </row>
-    <row r="8" spans="1:26">
+      <c r="AA7" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="8" spans="1:27">
       <c r="A8">
         <v>107</v>
       </c>
@@ -1141,8 +1230,11 @@
       <c r="Z8" s="1" t="s">
         <v>85</v>
       </c>
-    </row>
-    <row r="9" spans="1:26">
+      <c r="AA8" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="9" spans="1:27">
       <c r="A9">
         <v>108</v>
       </c>
@@ -1197,8 +1289,11 @@
       <c r="Z9" s="1" t="s">
         <v>85</v>
       </c>
-    </row>
-    <row r="10" spans="1:26">
+      <c r="AA9" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="10" spans="1:27">
       <c r="A10">
         <v>109</v>
       </c>
@@ -1253,8 +1348,11 @@
       <c r="Z10" s="1" t="s">
         <v>85</v>
       </c>
-    </row>
-    <row r="11" spans="1:26">
+      <c r="AA10" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="11" spans="1:27">
       <c r="A11">
         <v>110</v>
       </c>
@@ -1288,8 +1386,11 @@
       <c r="Z11" s="1" t="s">
         <v>85</v>
       </c>
-    </row>
-    <row r="12" spans="1:26">
+      <c r="AA11" t="s">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="12" spans="1:27">
       <c r="A12">
         <v>201</v>
       </c>
@@ -1314,8 +1415,11 @@
       <c r="Z12" s="1" t="s">
         <v>86</v>
       </c>
-    </row>
-    <row r="13" spans="1:26">
+      <c r="AA12" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="13" spans="1:27">
       <c r="A13">
         <v>202</v>
       </c>
@@ -1349,8 +1453,11 @@
       <c r="Z13" s="1" t="s">
         <v>86</v>
       </c>
-    </row>
-    <row r="14" spans="1:26">
+      <c r="AA13" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="14" spans="1:27">
       <c r="A14">
         <v>203</v>
       </c>
@@ -1390,8 +1497,11 @@
       <c r="Z14" s="1" t="s">
         <v>86</v>
       </c>
-    </row>
-    <row r="15" spans="1:26">
+      <c r="AA14" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="15" spans="1:27">
       <c r="A15">
         <v>204</v>
       </c>
@@ -1446,8 +1556,11 @@
       <c r="Z15" s="1" t="s">
         <v>86</v>
       </c>
-    </row>
-    <row r="16" spans="1:26">
+      <c r="AA15" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="16" spans="1:27">
       <c r="A16">
         <v>205</v>
       </c>
@@ -1502,8 +1615,11 @@
       <c r="Z16" s="1" t="s">
         <v>86</v>
       </c>
-    </row>
-    <row r="17" spans="1:26">
+      <c r="AA16" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="17" spans="1:27">
       <c r="A17">
         <v>206</v>
       </c>
@@ -1558,8 +1674,11 @@
       <c r="Z17" s="1" t="s">
         <v>86</v>
       </c>
-    </row>
-    <row r="18" spans="1:26">
+      <c r="AA17" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="18" spans="1:27">
       <c r="A18">
         <v>207</v>
       </c>
@@ -1614,8 +1733,11 @@
       <c r="Z18" s="1" t="s">
         <v>86</v>
       </c>
-    </row>
-    <row r="19" spans="1:26">
+      <c r="AA18" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="19" spans="1:27">
       <c r="A19">
         <v>208</v>
       </c>
@@ -1670,8 +1792,11 @@
       <c r="Z19" s="1" t="s">
         <v>86</v>
       </c>
-    </row>
-    <row r="20" spans="1:26">
+      <c r="AA19" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="20" spans="1:27">
       <c r="A20">
         <v>209</v>
       </c>
@@ -1726,8 +1851,11 @@
       <c r="Z20" s="1" t="s">
         <v>86</v>
       </c>
-    </row>
-    <row r="21" spans="1:26">
+      <c r="AA20" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="21" spans="1:27">
       <c r="A21">
         <v>210</v>
       </c>
@@ -1761,8 +1889,11 @@
       <c r="Z21" s="1" t="s">
         <v>86</v>
       </c>
-    </row>
-    <row r="22" spans="1:26">
+      <c r="AA21" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="22" spans="1:27">
       <c r="A22">
         <v>301</v>
       </c>
@@ -1793,8 +1924,11 @@
       <c r="Z22" s="1" t="s">
         <v>87</v>
       </c>
-    </row>
-    <row r="23" spans="1:26">
+      <c r="AA22" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="23" spans="1:27">
       <c r="A23">
         <v>302</v>
       </c>
@@ -1834,8 +1968,11 @@
       <c r="Z23" s="1" t="s">
         <v>87</v>
       </c>
-    </row>
-    <row r="24" spans="1:26">
+      <c r="AA23" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="24" spans="1:27">
       <c r="A24">
         <v>303</v>
       </c>
@@ -1881,8 +2018,11 @@
       <c r="Z24" s="1" t="s">
         <v>87</v>
       </c>
-    </row>
-    <row r="25" spans="1:26">
+      <c r="AA24" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="25" spans="1:27">
       <c r="A25">
         <v>304</v>
       </c>
@@ -1937,8 +2077,11 @@
       <c r="Z25" s="1" t="s">
         <v>87</v>
       </c>
-    </row>
-    <row r="26" spans="1:26">
+      <c r="AA25" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="26" spans="1:27">
       <c r="A26">
         <v>305</v>
       </c>
@@ -1993,8 +2136,11 @@
       <c r="Z26" s="1" t="s">
         <v>87</v>
       </c>
-    </row>
-    <row r="27" spans="1:26">
+      <c r="AA26" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="27" spans="1:27">
       <c r="A27">
         <v>306</v>
       </c>
@@ -2055,8 +2201,11 @@
       <c r="Z27" s="1" t="s">
         <v>87</v>
       </c>
-    </row>
-    <row r="28" spans="1:26">
+      <c r="AA27" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="28" spans="1:27">
       <c r="A28">
         <v>307</v>
       </c>
@@ -2135,8 +2284,11 @@
       <c r="Z28" s="1" t="s">
         <v>87</v>
       </c>
-    </row>
-    <row r="29" spans="1:26">
+      <c r="AA28" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="29" spans="1:27">
       <c r="A29">
         <v>308</v>
       </c>
@@ -2215,8 +2367,11 @@
       <c r="Z29" s="1" t="s">
         <v>87</v>
       </c>
-    </row>
-    <row r="30" spans="1:26">
+      <c r="AA29" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="30" spans="1:27">
       <c r="A30">
         <v>309</v>
       </c>
@@ -2295,8 +2450,11 @@
       <c r="Z30" s="1" t="s">
         <v>87</v>
       </c>
-    </row>
-    <row r="31" spans="1:26">
+      <c r="AA30" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="31" spans="1:27">
       <c r="A31">
         <v>310</v>
       </c>
@@ -2348,8 +2506,11 @@
       <c r="Z31" s="1" t="s">
         <v>87</v>
       </c>
-    </row>
-    <row r="32" spans="1:26">
+      <c r="AA31" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="32" spans="1:27">
       <c r="A32">
         <v>401</v>
       </c>
@@ -2386,8 +2547,11 @@
       <c r="Z32" s="1" t="s">
         <v>88</v>
       </c>
-    </row>
-    <row r="33" spans="1:26">
+      <c r="AA32" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="33" spans="1:27">
       <c r="A33">
         <v>402</v>
       </c>
@@ -2433,8 +2597,11 @@
       <c r="Z33" s="1" t="s">
         <v>88</v>
       </c>
-    </row>
-    <row r="34" spans="1:26">
+      <c r="AA33" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="34" spans="1:27">
       <c r="A34">
         <v>403</v>
       </c>
@@ -2480,8 +2647,11 @@
       <c r="Z34" s="1" t="s">
         <v>88</v>
       </c>
-    </row>
-    <row r="35" spans="1:26">
+      <c r="AA34" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="35" spans="1:27">
       <c r="A35">
         <v>404</v>
       </c>
@@ -2536,8 +2706,11 @@
       <c r="Z35" s="1" t="s">
         <v>88</v>
       </c>
-    </row>
-    <row r="36" spans="1:26">
+      <c r="AA35" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="36" spans="1:27">
       <c r="A36">
         <v>405</v>
       </c>
@@ -2598,8 +2771,11 @@
       <c r="Z36" s="1" t="s">
         <v>88</v>
       </c>
-    </row>
-    <row r="37" spans="1:26">
+      <c r="AA36" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="37" spans="1:27">
       <c r="A37">
         <v>406</v>
       </c>
@@ -2660,8 +2836,11 @@
       <c r="Z37" s="1" t="s">
         <v>88</v>
       </c>
-    </row>
-    <row r="38" spans="1:26">
+      <c r="AA37" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="38" spans="1:27">
       <c r="A38">
         <v>407</v>
       </c>
@@ -2722,8 +2901,11 @@
       <c r="Z38" s="1" t="s">
         <v>88</v>
       </c>
-    </row>
-    <row r="39" spans="1:26">
+      <c r="AA38" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="39" spans="1:27">
       <c r="A39">
         <v>408</v>
       </c>
@@ -2784,8 +2966,11 @@
       <c r="Z39" s="1" t="s">
         <v>88</v>
       </c>
-    </row>
-    <row r="40" spans="1:26">
+      <c r="AA39" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="40" spans="1:27">
       <c r="A40">
         <v>409</v>
       </c>
@@ -2846,8 +3031,11 @@
       <c r="Z40" s="1" t="s">
         <v>88</v>
       </c>
-    </row>
-    <row r="41" spans="1:26">
+      <c r="AA40" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="41" spans="1:27">
       <c r="A41">
         <v>410</v>
       </c>
@@ -2889,6 +3077,9 @@
       </c>
       <c r="Z41" s="1" t="s">
         <v>88</v>
+      </c>
+      <c r="AA41" t="s">
+        <v>104</v>
       </c>
     </row>
   </sheetData>

--- a/Assets/Excel/BuildingUpgradeSO.xlsx
+++ b/Assets/Excel/BuildingUpgradeSO.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Users\User\TeamProject_CheerUpMyHero\Assets\Excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D820F46D-946F-49E8-8BC5-2230F8E0D6D6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0F5B880C-AAC9-418B-A38B-86BCCA764C07}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{529EFE37-1A1C-40A3-AFC4-E608165EEB57}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="365" uniqueCount="105">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="370" uniqueCount="107">
   <si>
     <t>idNumber</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -400,6 +400,12 @@
   <si>
     <t>BuildingImages/Barracks_3</t>
     <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>CanSummonRareUnits</t>
+  </si>
+  <si>
+    <t>CanSummonEpicUnits</t>
   </si>
 </sst>
 </file>
@@ -2591,6 +2597,15 @@
       <c r="O33">
         <v>5</v>
       </c>
+      <c r="P33" t="s">
+        <v>105</v>
+      </c>
+      <c r="Q33">
+        <v>1</v>
+      </c>
+      <c r="R33">
+        <v>1</v>
+      </c>
       <c r="Y33" s="1" t="s">
         <v>66</v>
       </c>
@@ -2641,6 +2656,15 @@
       <c r="O34">
         <v>5</v>
       </c>
+      <c r="P34" t="s">
+        <v>105</v>
+      </c>
+      <c r="Q34">
+        <v>1</v>
+      </c>
+      <c r="R34">
+        <v>1</v>
+      </c>
       <c r="Y34" s="1" t="s">
         <v>67</v>
       </c>
@@ -2695,10 +2719,10 @@
         <v>81</v>
       </c>
       <c r="Q35">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="R35">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Y35" s="1" t="s">
         <v>68</v>
@@ -2760,10 +2784,10 @@
         <v>81</v>
       </c>
       <c r="Q36">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="R36">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Y36" s="1" t="s">
         <v>69</v>
@@ -2825,10 +2849,10 @@
         <v>81</v>
       </c>
       <c r="Q37">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="R37">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Y37" s="1" t="s">
         <v>70</v>
@@ -2890,10 +2914,19 @@
         <v>81</v>
       </c>
       <c r="Q38">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="R38">
-        <v>2</v>
+        <v>4</v>
+      </c>
+      <c r="S38" t="s">
+        <v>106</v>
+      </c>
+      <c r="T38">
+        <v>1</v>
+      </c>
+      <c r="U38">
+        <v>1</v>
       </c>
       <c r="Y38" s="1" t="s">
         <v>71</v>
@@ -2955,10 +2988,19 @@
         <v>81</v>
       </c>
       <c r="Q39">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="R39">
-        <v>2</v>
+        <v>4</v>
+      </c>
+      <c r="S39" t="s">
+        <v>106</v>
+      </c>
+      <c r="T39">
+        <v>1</v>
+      </c>
+      <c r="U39">
+        <v>1</v>
       </c>
       <c r="Y39" s="1" t="s">
         <v>72</v>
@@ -3020,10 +3062,19 @@
         <v>81</v>
       </c>
       <c r="Q40">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="R40">
-        <v>2</v>
+        <v>4</v>
+      </c>
+      <c r="S40" t="s">
+        <v>106</v>
+      </c>
+      <c r="T40">
+        <v>1</v>
+      </c>
+      <c r="U40">
+        <v>1</v>
       </c>
       <c r="Y40" s="1" t="s">
         <v>73</v>
@@ -3058,19 +3109,19 @@
         <v>81</v>
       </c>
       <c r="Q41">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="R41">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="S41" t="s">
         <v>82</v>
       </c>
       <c r="T41">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="U41">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Y41" s="1" t="s">
         <v>74</v>

--- a/Assets/Excel/BuildingUpgradeSO.xlsx
+++ b/Assets/Excel/BuildingUpgradeSO.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Users\User\TeamProject_CheerUpMyHero\Assets\Excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0F5B880C-AAC9-418B-A38B-86BCCA764C07}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2582DFB2-B7F9-4467-9DB7-5077E062EB43}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{529EFE37-1A1C-40A3-AFC4-E608165EEB57}"/>
   </bookViews>
@@ -948,10 +948,10 @@
         <v>75</v>
       </c>
       <c r="Q3">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="R3">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="Y3" s="1" t="s">
         <v>19</v>
@@ -995,10 +995,10 @@
         <v>75</v>
       </c>
       <c r="Q4">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="R4">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="Y4" s="1" t="s">
         <v>20</v>
@@ -1048,10 +1048,10 @@
         <v>75</v>
       </c>
       <c r="Q5">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="R5">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="Y5" s="1" t="s">
         <v>21</v>
@@ -1107,10 +1107,10 @@
         <v>75</v>
       </c>
       <c r="Q6">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="R6">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="Y6" s="1" t="s">
         <v>22</v>
@@ -1166,10 +1166,10 @@
         <v>75</v>
       </c>
       <c r="Q7">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="R7">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="Y7" s="1" t="s">
         <v>23</v>
@@ -1225,10 +1225,10 @@
         <v>75</v>
       </c>
       <c r="Q8">
-        <v>30</v>
+        <v>35</v>
       </c>
       <c r="R8">
-        <v>30</v>
+        <v>35</v>
       </c>
       <c r="Y8" s="1" t="s">
         <v>24</v>
@@ -1284,10 +1284,10 @@
         <v>75</v>
       </c>
       <c r="Q9">
-        <v>35</v>
+        <v>40</v>
       </c>
       <c r="R9">
-        <v>35</v>
+        <v>40</v>
       </c>
       <c r="Y9" s="1" t="s">
         <v>25</v>
@@ -1343,10 +1343,10 @@
         <v>75</v>
       </c>
       <c r="Q10">
-        <v>40</v>
+        <v>45</v>
       </c>
       <c r="R10">
-        <v>40</v>
+        <v>45</v>
       </c>
       <c r="Y10" s="1" t="s">
         <v>26</v>
@@ -1381,10 +1381,10 @@
         <v>75</v>
       </c>
       <c r="Q11">
-        <v>50</v>
+        <v>55</v>
       </c>
       <c r="R11">
-        <v>50</v>
+        <v>55</v>
       </c>
       <c r="Y11" s="1" t="s">
         <v>27</v>

--- a/Assets/Excel/BuildingUpgradeSO.xlsx
+++ b/Assets/Excel/BuildingUpgradeSO.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Users\User\TeamProject_CheerUpMyHero\Assets\Excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2582DFB2-B7F9-4467-9DB7-5077E062EB43}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9654631B-3D35-4B1E-9D8D-0DD3E23E6A41}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{529EFE37-1A1C-40A3-AFC4-E608165EEB57}"/>
+    <workbookView xWindow="1275" yWindow="-120" windowWidth="27645" windowHeight="16440" xr2:uid="{529EFE37-1A1C-40A3-AFC4-E608165EEB57}"/>
   </bookViews>
   <sheets>
     <sheet name="BuildingUpgrade" sheetId="1" r:id="rId1"/>
@@ -92,9 +92,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>농장을 건설하여 안정적으로 식량을 확보합니다.</t>
-  </si>
-  <si>
     <t>농장1레벨입니다.</t>
   </si>
   <si>
@@ -211,14 +208,6 @@
     <t>MagicStoneFindChance</t>
   </si>
   <si>
-    <t>벌목장을 건설하여 안정적으로 목재를 확보합니다.</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>탄광을 건설하여 안정적으로 철괴를 확보합니다.</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>탄광1레벨입니다.</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -251,10 +240,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>병영을 건설하여 전투에 투입할 수 있는 최대 인구 수를 늘립니다.</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>병영1레벨입니다.</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -406,6 +391,22 @@
   </si>
   <si>
     <t>CanSummonEpicUnits</t>
+  </si>
+  <si>
+    <t>안정적으로 식량을 확보합니다.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>안정적으로 목재를 확보합니다.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>안정적으로 철괴를 확보합니다.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>전투에 투입할 수 있는 유닛의 쿨타임을 감소시킵니다.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
 </file>
@@ -845,46 +846,46 @@
         <v>13</v>
       </c>
       <c r="N1" t="s">
+        <v>40</v>
+      </c>
+      <c r="O1" t="s">
         <v>41</v>
       </c>
-      <c r="O1" t="s">
+      <c r="P1" t="s">
         <v>42</v>
       </c>
-      <c r="P1" t="s">
+      <c r="Q1" t="s">
         <v>43</v>
       </c>
-      <c r="Q1" t="s">
+      <c r="R1" t="s">
         <v>44</v>
       </c>
-      <c r="R1" t="s">
+      <c r="S1" t="s">
         <v>45</v>
       </c>
-      <c r="S1" t="s">
+      <c r="T1" t="s">
         <v>46</v>
       </c>
-      <c r="T1" t="s">
+      <c r="U1" t="s">
         <v>47</v>
       </c>
-      <c r="U1" t="s">
+      <c r="V1" t="s">
         <v>48</v>
       </c>
-      <c r="V1" t="s">
+      <c r="W1" t="s">
         <v>49</v>
       </c>
-      <c r="W1" t="s">
+      <c r="X1" t="s">
         <v>50</v>
-      </c>
-      <c r="X1" t="s">
-        <v>51</v>
       </c>
       <c r="Y1" s="1" t="s">
         <v>4</v>
       </c>
       <c r="Z1" s="2" t="s">
-        <v>89</v>
+        <v>85</v>
       </c>
       <c r="AA1" s="3" t="s">
-        <v>91</v>
+        <v>87</v>
       </c>
     </row>
     <row r="2" spans="1:27">
@@ -907,13 +908,13 @@
         <v>100</v>
       </c>
       <c r="Y2" s="1" t="s">
-        <v>18</v>
+        <v>103</v>
       </c>
       <c r="Z2" s="1" t="s">
-        <v>85</v>
+        <v>81</v>
       </c>
       <c r="AA2" t="s">
-        <v>92</v>
+        <v>88</v>
       </c>
     </row>
     <row r="3" spans="1:27">
@@ -936,7 +937,7 @@
         <v>200</v>
       </c>
       <c r="M3" t="s">
-        <v>84</v>
+        <v>80</v>
       </c>
       <c r="N3">
         <v>500</v>
@@ -945,7 +946,7 @@
         <v>500</v>
       </c>
       <c r="P3" t="s">
-        <v>75</v>
+        <v>71</v>
       </c>
       <c r="Q3">
         <v>10</v>
@@ -954,13 +955,13 @@
         <v>10</v>
       </c>
       <c r="Y3" s="1" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="Z3" s="1" t="s">
-        <v>85</v>
+        <v>81</v>
       </c>
       <c r="AA3" t="s">
-        <v>93</v>
+        <v>89</v>
       </c>
     </row>
     <row r="4" spans="1:27">
@@ -983,7 +984,7 @@
         <v>450</v>
       </c>
       <c r="M4" t="s">
-        <v>84</v>
+        <v>80</v>
       </c>
       <c r="N4">
         <v>750</v>
@@ -992,7 +993,7 @@
         <v>750</v>
       </c>
       <c r="P4" t="s">
-        <v>75</v>
+        <v>71</v>
       </c>
       <c r="Q4">
         <v>15</v>
@@ -1001,13 +1002,13 @@
         <v>15</v>
       </c>
       <c r="Y4" s="1" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="Z4" s="1" t="s">
-        <v>85</v>
+        <v>81</v>
       </c>
       <c r="AA4" t="s">
-        <v>93</v>
+        <v>89</v>
       </c>
     </row>
     <row r="5" spans="1:27">
@@ -1036,7 +1037,7 @@
         <v>50</v>
       </c>
       <c r="M5" t="s">
-        <v>84</v>
+        <v>80</v>
       </c>
       <c r="N5">
         <v>1000</v>
@@ -1045,7 +1046,7 @@
         <v>1000</v>
       </c>
       <c r="P5" t="s">
-        <v>75</v>
+        <v>71</v>
       </c>
       <c r="Q5">
         <v>20</v>
@@ -1054,13 +1055,13 @@
         <v>20</v>
       </c>
       <c r="Y5" s="1" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="Z5" s="1" t="s">
-        <v>85</v>
+        <v>81</v>
       </c>
       <c r="AA5" t="s">
-        <v>93</v>
+        <v>89</v>
       </c>
     </row>
     <row r="6" spans="1:27">
@@ -1095,7 +1096,7 @@
         <v>20</v>
       </c>
       <c r="M6" t="s">
-        <v>84</v>
+        <v>80</v>
       </c>
       <c r="N6">
         <v>1250</v>
@@ -1104,7 +1105,7 @@
         <v>1250</v>
       </c>
       <c r="P6" t="s">
-        <v>75</v>
+        <v>71</v>
       </c>
       <c r="Q6">
         <v>25</v>
@@ -1113,13 +1114,13 @@
         <v>25</v>
       </c>
       <c r="Y6" s="1" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="Z6" s="1" t="s">
-        <v>85</v>
+        <v>81</v>
       </c>
       <c r="AA6" t="s">
-        <v>93</v>
+        <v>89</v>
       </c>
     </row>
     <row r="7" spans="1:27">
@@ -1154,7 +1155,7 @@
         <v>35</v>
       </c>
       <c r="M7" t="s">
-        <v>84</v>
+        <v>80</v>
       </c>
       <c r="N7">
         <v>1500</v>
@@ -1163,7 +1164,7 @@
         <v>1500</v>
       </c>
       <c r="P7" t="s">
-        <v>75</v>
+        <v>71</v>
       </c>
       <c r="Q7">
         <v>30</v>
@@ -1172,13 +1173,13 @@
         <v>30</v>
       </c>
       <c r="Y7" s="1" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="Z7" s="1" t="s">
-        <v>85</v>
+        <v>81</v>
       </c>
       <c r="AA7" t="s">
-        <v>95</v>
+        <v>91</v>
       </c>
     </row>
     <row r="8" spans="1:27">
@@ -1213,7 +1214,7 @@
         <v>50</v>
       </c>
       <c r="M8" t="s">
-        <v>84</v>
+        <v>80</v>
       </c>
       <c r="N8">
         <v>1750</v>
@@ -1222,7 +1223,7 @@
         <v>1750</v>
       </c>
       <c r="P8" t="s">
-        <v>75</v>
+        <v>71</v>
       </c>
       <c r="Q8">
         <v>35</v>
@@ -1231,13 +1232,13 @@
         <v>35</v>
       </c>
       <c r="Y8" s="1" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="Z8" s="1" t="s">
-        <v>85</v>
+        <v>81</v>
       </c>
       <c r="AA8" t="s">
-        <v>95</v>
+        <v>91</v>
       </c>
     </row>
     <row r="9" spans="1:27">
@@ -1272,7 +1273,7 @@
         <v>75</v>
       </c>
       <c r="M9" t="s">
-        <v>84</v>
+        <v>80</v>
       </c>
       <c r="N9">
         <v>2000</v>
@@ -1281,7 +1282,7 @@
         <v>2000</v>
       </c>
       <c r="P9" t="s">
-        <v>75</v>
+        <v>71</v>
       </c>
       <c r="Q9">
         <v>40</v>
@@ -1290,13 +1291,13 @@
         <v>40</v>
       </c>
       <c r="Y9" s="1" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="Z9" s="1" t="s">
-        <v>85</v>
+        <v>81</v>
       </c>
       <c r="AA9" t="s">
-        <v>95</v>
+        <v>91</v>
       </c>
     </row>
     <row r="10" spans="1:27">
@@ -1331,7 +1332,7 @@
         <v>100</v>
       </c>
       <c r="M10" t="s">
-        <v>84</v>
+        <v>80</v>
       </c>
       <c r="N10">
         <v>2250</v>
@@ -1340,7 +1341,7 @@
         <v>2250</v>
       </c>
       <c r="P10" t="s">
-        <v>75</v>
+        <v>71</v>
       </c>
       <c r="Q10">
         <v>45</v>
@@ -1349,13 +1350,13 @@
         <v>45</v>
       </c>
       <c r="Y10" s="1" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="Z10" s="1" t="s">
-        <v>85</v>
+        <v>81</v>
       </c>
       <c r="AA10" t="s">
-        <v>95</v>
+        <v>91</v>
       </c>
     </row>
     <row r="11" spans="1:27">
@@ -1369,7 +1370,7 @@
         <v>9</v>
       </c>
       <c r="M11" t="s">
-        <v>84</v>
+        <v>80</v>
       </c>
       <c r="N11">
         <v>2500</v>
@@ -1378,7 +1379,7 @@
         <v>2500</v>
       </c>
       <c r="P11" t="s">
-        <v>75</v>
+        <v>71</v>
       </c>
       <c r="Q11">
         <v>55</v>
@@ -1387,13 +1388,13 @@
         <v>55</v>
       </c>
       <c r="Y11" s="1" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="Z11" s="1" t="s">
-        <v>85</v>
+        <v>81</v>
       </c>
       <c r="AA11" t="s">
-        <v>94</v>
+        <v>90</v>
       </c>
     </row>
     <row r="12" spans="1:27">
@@ -1401,7 +1402,7 @@
         <v>201</v>
       </c>
       <c r="B12" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C12">
         <v>0</v>
@@ -1416,13 +1417,13 @@
         <v>150</v>
       </c>
       <c r="Y12" s="1" t="s">
-        <v>53</v>
+        <v>104</v>
       </c>
       <c r="Z12" s="1" t="s">
-        <v>86</v>
+        <v>82</v>
       </c>
       <c r="AA12" t="s">
-        <v>92</v>
+        <v>88</v>
       </c>
     </row>
     <row r="13" spans="1:27">
@@ -1430,7 +1431,7 @@
         <v>202</v>
       </c>
       <c r="B13" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C13">
         <v>1</v>
@@ -1445,7 +1446,7 @@
         <v>300</v>
       </c>
       <c r="M13" t="s">
-        <v>76</v>
+        <v>72</v>
       </c>
       <c r="N13">
         <v>10</v>
@@ -1454,13 +1455,13 @@
         <v>10</v>
       </c>
       <c r="Y13" s="1" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="Z13" s="1" t="s">
-        <v>86</v>
+        <v>82</v>
       </c>
       <c r="AA13" t="s">
-        <v>96</v>
+        <v>92</v>
       </c>
     </row>
     <row r="14" spans="1:27">
@@ -1468,7 +1469,7 @@
         <v>203</v>
       </c>
       <c r="B14" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C14">
         <v>2</v>
@@ -1489,7 +1490,7 @@
         <v>50</v>
       </c>
       <c r="M14" t="s">
-        <v>76</v>
+        <v>72</v>
       </c>
       <c r="N14">
         <v>20</v>
@@ -1498,13 +1499,13 @@
         <v>20</v>
       </c>
       <c r="Y14" s="1" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="Z14" s="1" t="s">
-        <v>86</v>
+        <v>82</v>
       </c>
       <c r="AA14" t="s">
-        <v>96</v>
+        <v>92</v>
       </c>
     </row>
     <row r="15" spans="1:27">
@@ -1512,7 +1513,7 @@
         <v>204</v>
       </c>
       <c r="B15" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C15">
         <v>3</v>
@@ -1539,7 +1540,7 @@
         <v>20</v>
       </c>
       <c r="M15" t="s">
-        <v>76</v>
+        <v>72</v>
       </c>
       <c r="N15">
         <v>30</v>
@@ -1548,7 +1549,7 @@
         <v>30</v>
       </c>
       <c r="P15" t="s">
-        <v>77</v>
+        <v>73</v>
       </c>
       <c r="Q15">
         <v>10</v>
@@ -1557,13 +1558,13 @@
         <v>10</v>
       </c>
       <c r="Y15" s="1" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="Z15" s="1" t="s">
-        <v>86</v>
+        <v>82</v>
       </c>
       <c r="AA15" t="s">
-        <v>96</v>
+        <v>92</v>
       </c>
     </row>
     <row r="16" spans="1:27">
@@ -1571,7 +1572,7 @@
         <v>205</v>
       </c>
       <c r="B16" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C16">
         <v>4</v>
@@ -1598,7 +1599,7 @@
         <v>35</v>
       </c>
       <c r="M16" t="s">
-        <v>76</v>
+        <v>72</v>
       </c>
       <c r="N16">
         <v>40</v>
@@ -1607,7 +1608,7 @@
         <v>40</v>
       </c>
       <c r="P16" t="s">
-        <v>77</v>
+        <v>73</v>
       </c>
       <c r="Q16">
         <v>10</v>
@@ -1616,13 +1617,13 @@
         <v>10</v>
       </c>
       <c r="Y16" s="1" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="Z16" s="1" t="s">
-        <v>86</v>
+        <v>82</v>
       </c>
       <c r="AA16" t="s">
-        <v>96</v>
+        <v>92</v>
       </c>
     </row>
     <row r="17" spans="1:27">
@@ -1630,7 +1631,7 @@
         <v>206</v>
       </c>
       <c r="B17" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C17">
         <v>5</v>
@@ -1657,7 +1658,7 @@
         <v>50</v>
       </c>
       <c r="M17" t="s">
-        <v>76</v>
+        <v>72</v>
       </c>
       <c r="N17">
         <v>50</v>
@@ -1666,7 +1667,7 @@
         <v>50</v>
       </c>
       <c r="P17" t="s">
-        <v>77</v>
+        <v>73</v>
       </c>
       <c r="Q17">
         <v>10</v>
@@ -1675,13 +1676,13 @@
         <v>10</v>
       </c>
       <c r="Y17" s="1" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="Z17" s="1" t="s">
-        <v>86</v>
+        <v>82</v>
       </c>
       <c r="AA17" t="s">
-        <v>97</v>
+        <v>93</v>
       </c>
     </row>
     <row r="18" spans="1:27">
@@ -1689,7 +1690,7 @@
         <v>207</v>
       </c>
       <c r="B18" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C18">
         <v>6</v>
@@ -1716,7 +1717,7 @@
         <v>75</v>
       </c>
       <c r="M18" t="s">
-        <v>76</v>
+        <v>72</v>
       </c>
       <c r="N18">
         <v>60</v>
@@ -1725,7 +1726,7 @@
         <v>60</v>
       </c>
       <c r="P18" t="s">
-        <v>77</v>
+        <v>73</v>
       </c>
       <c r="Q18">
         <v>20</v>
@@ -1734,13 +1735,13 @@
         <v>20</v>
       </c>
       <c r="Y18" s="1" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="Z18" s="1" t="s">
-        <v>86</v>
+        <v>82</v>
       </c>
       <c r="AA18" t="s">
-        <v>97</v>
+        <v>93</v>
       </c>
     </row>
     <row r="19" spans="1:27">
@@ -1748,7 +1749,7 @@
         <v>208</v>
       </c>
       <c r="B19" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C19">
         <v>7</v>
@@ -1775,7 +1776,7 @@
         <v>100</v>
       </c>
       <c r="M19" t="s">
-        <v>76</v>
+        <v>72</v>
       </c>
       <c r="N19">
         <v>70</v>
@@ -1784,7 +1785,7 @@
         <v>70</v>
       </c>
       <c r="P19" t="s">
-        <v>77</v>
+        <v>73</v>
       </c>
       <c r="Q19">
         <v>20</v>
@@ -1793,13 +1794,13 @@
         <v>20</v>
       </c>
       <c r="Y19" s="1" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="Z19" s="1" t="s">
-        <v>86</v>
+        <v>82</v>
       </c>
       <c r="AA19" t="s">
-        <v>97</v>
+        <v>93</v>
       </c>
     </row>
     <row r="20" spans="1:27">
@@ -1807,7 +1808,7 @@
         <v>209</v>
       </c>
       <c r="B20" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C20">
         <v>8</v>
@@ -1834,7 +1835,7 @@
         <v>150</v>
       </c>
       <c r="M20" t="s">
-        <v>76</v>
+        <v>72</v>
       </c>
       <c r="N20">
         <v>80</v>
@@ -1843,7 +1844,7 @@
         <v>80</v>
       </c>
       <c r="P20" t="s">
-        <v>77</v>
+        <v>73</v>
       </c>
       <c r="Q20">
         <v>20</v>
@@ -1852,13 +1853,13 @@
         <v>20</v>
       </c>
       <c r="Y20" s="1" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="Z20" s="1" t="s">
-        <v>86</v>
+        <v>82</v>
       </c>
       <c r="AA20" t="s">
-        <v>97</v>
+        <v>93</v>
       </c>
     </row>
     <row r="21" spans="1:27">
@@ -1866,13 +1867,13 @@
         <v>210</v>
       </c>
       <c r="B21" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C21">
         <v>9</v>
       </c>
       <c r="M21" t="s">
-        <v>76</v>
+        <v>72</v>
       </c>
       <c r="N21">
         <v>100</v>
@@ -1881,7 +1882,7 @@
         <v>100</v>
       </c>
       <c r="P21" t="s">
-        <v>77</v>
+        <v>73</v>
       </c>
       <c r="Q21">
         <v>30</v>
@@ -1890,13 +1891,13 @@
         <v>30</v>
       </c>
       <c r="Y21" s="1" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="Z21" s="1" t="s">
-        <v>86</v>
+        <v>82</v>
       </c>
       <c r="AA21" t="s">
-        <v>98</v>
+        <v>94</v>
       </c>
     </row>
     <row r="22" spans="1:27">
@@ -1904,7 +1905,7 @@
         <v>301</v>
       </c>
       <c r="B22" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="C22">
         <v>0</v>
@@ -1925,13 +1926,13 @@
         <v>10</v>
       </c>
       <c r="Y22" s="1" t="s">
-        <v>54</v>
+        <v>105</v>
       </c>
       <c r="Z22" s="1" t="s">
-        <v>87</v>
+        <v>83</v>
       </c>
       <c r="AA22" t="s">
-        <v>92</v>
+        <v>88</v>
       </c>
     </row>
     <row r="23" spans="1:27">
@@ -1939,7 +1940,7 @@
         <v>302</v>
       </c>
       <c r="B23" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="C23">
         <v>1</v>
@@ -1960,7 +1961,7 @@
         <v>50</v>
       </c>
       <c r="M23" t="s">
-        <v>78</v>
+        <v>74</v>
       </c>
       <c r="N23">
         <v>5</v>
@@ -1969,13 +1970,13 @@
         <v>5</v>
       </c>
       <c r="Y23" s="1" t="s">
-        <v>55</v>
+        <v>52</v>
       </c>
       <c r="Z23" s="1" t="s">
-        <v>87</v>
+        <v>83</v>
       </c>
       <c r="AA23" t="s">
-        <v>99</v>
+        <v>95</v>
       </c>
     </row>
     <row r="24" spans="1:27">
@@ -1983,7 +1984,7 @@
         <v>303</v>
       </c>
       <c r="B24" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="C24">
         <v>2</v>
@@ -2010,7 +2011,7 @@
         <v>30</v>
       </c>
       <c r="M24" t="s">
-        <v>78</v>
+        <v>74</v>
       </c>
       <c r="N24">
         <v>10</v>
@@ -2019,13 +2020,13 @@
         <v>10</v>
       </c>
       <c r="Y24" s="1" t="s">
-        <v>56</v>
+        <v>53</v>
       </c>
       <c r="Z24" s="1" t="s">
-        <v>87</v>
+        <v>83</v>
       </c>
       <c r="AA24" t="s">
-        <v>99</v>
+        <v>95</v>
       </c>
     </row>
     <row r="25" spans="1:27">
@@ -2033,7 +2034,7 @@
         <v>304</v>
       </c>
       <c r="B25" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="C25">
         <v>3</v>
@@ -2060,7 +2061,7 @@
         <v>60</v>
       </c>
       <c r="M25" t="s">
-        <v>78</v>
+        <v>74</v>
       </c>
       <c r="N25">
         <v>15</v>
@@ -2069,7 +2070,7 @@
         <v>15</v>
       </c>
       <c r="P25" t="s">
-        <v>79</v>
+        <v>75</v>
       </c>
       <c r="Q25">
         <v>5</v>
@@ -2078,13 +2079,13 @@
         <v>5</v>
       </c>
       <c r="Y25" s="1" t="s">
-        <v>57</v>
+        <v>54</v>
       </c>
       <c r="Z25" s="1" t="s">
-        <v>87</v>
+        <v>83</v>
       </c>
       <c r="AA25" t="s">
-        <v>99</v>
+        <v>95</v>
       </c>
     </row>
     <row r="26" spans="1:27">
@@ -2092,7 +2093,7 @@
         <v>305</v>
       </c>
       <c r="B26" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="C26">
         <v>4</v>
@@ -2119,7 +2120,7 @@
         <v>100</v>
       </c>
       <c r="M26" t="s">
-        <v>78</v>
+        <v>74</v>
       </c>
       <c r="N26">
         <v>20</v>
@@ -2128,7 +2129,7 @@
         <v>20</v>
       </c>
       <c r="P26" t="s">
-        <v>79</v>
+        <v>75</v>
       </c>
       <c r="Q26">
         <v>5</v>
@@ -2137,13 +2138,13 @@
         <v>5</v>
       </c>
       <c r="Y26" s="1" t="s">
-        <v>58</v>
+        <v>55</v>
       </c>
       <c r="Z26" s="1" t="s">
-        <v>87</v>
+        <v>83</v>
       </c>
       <c r="AA26" t="s">
-        <v>99</v>
+        <v>95</v>
       </c>
     </row>
     <row r="27" spans="1:27">
@@ -2151,7 +2152,7 @@
         <v>306</v>
       </c>
       <c r="B27" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="C27">
         <v>5</v>
@@ -2178,13 +2179,13 @@
         <v>150</v>
       </c>
       <c r="K27" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="L27">
         <v>1</v>
       </c>
       <c r="M27" t="s">
-        <v>78</v>
+        <v>74</v>
       </c>
       <c r="N27">
         <v>25</v>
@@ -2193,7 +2194,7 @@
         <v>25</v>
       </c>
       <c r="P27" t="s">
-        <v>79</v>
+        <v>75</v>
       </c>
       <c r="Q27">
         <v>5</v>
@@ -2202,13 +2203,13 @@
         <v>5</v>
       </c>
       <c r="Y27" s="1" t="s">
-        <v>59</v>
+        <v>56</v>
       </c>
       <c r="Z27" s="1" t="s">
-        <v>87</v>
+        <v>83</v>
       </c>
       <c r="AA27" t="s">
-        <v>100</v>
+        <v>96</v>
       </c>
     </row>
     <row r="28" spans="1:27">
@@ -2216,7 +2217,7 @@
         <v>307</v>
       </c>
       <c r="B28" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="C28">
         <v>6</v>
@@ -2243,13 +2244,13 @@
         <v>200</v>
       </c>
       <c r="K28" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="L28">
         <v>10</v>
       </c>
       <c r="M28" t="s">
-        <v>78</v>
+        <v>74</v>
       </c>
       <c r="N28">
         <v>30</v>
@@ -2258,7 +2259,7 @@
         <v>30</v>
       </c>
       <c r="P28" t="s">
-        <v>79</v>
+        <v>75</v>
       </c>
       <c r="Q28">
         <v>10</v>
@@ -2267,7 +2268,7 @@
         <v>10</v>
       </c>
       <c r="S28" t="s">
-        <v>80</v>
+        <v>76</v>
       </c>
       <c r="T28">
         <v>10</v>
@@ -2276,7 +2277,7 @@
         <v>10</v>
       </c>
       <c r="V28" t="s">
-        <v>83</v>
+        <v>79</v>
       </c>
       <c r="W28">
         <v>1</v>
@@ -2285,13 +2286,13 @@
         <v>5</v>
       </c>
       <c r="Y28" s="1" t="s">
-        <v>60</v>
+        <v>57</v>
       </c>
       <c r="Z28" s="1" t="s">
-        <v>87</v>
+        <v>83</v>
       </c>
       <c r="AA28" t="s">
-        <v>100</v>
+        <v>96</v>
       </c>
     </row>
     <row r="29" spans="1:27">
@@ -2299,7 +2300,7 @@
         <v>308</v>
       </c>
       <c r="B29" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="C29">
         <v>7</v>
@@ -2326,13 +2327,13 @@
         <v>250</v>
       </c>
       <c r="K29" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="L29">
         <v>25</v>
       </c>
       <c r="M29" t="s">
-        <v>78</v>
+        <v>74</v>
       </c>
       <c r="N29">
         <v>35</v>
@@ -2341,7 +2342,7 @@
         <v>35</v>
       </c>
       <c r="P29" t="s">
-        <v>79</v>
+        <v>75</v>
       </c>
       <c r="Q29">
         <v>10</v>
@@ -2350,7 +2351,7 @@
         <v>10</v>
       </c>
       <c r="S29" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="T29">
         <v>20</v>
@@ -2359,7 +2360,7 @@
         <v>20</v>
       </c>
       <c r="V29" t="s">
-        <v>83</v>
+        <v>79</v>
       </c>
       <c r="W29">
         <v>3</v>
@@ -2368,13 +2369,13 @@
         <v>8</v>
       </c>
       <c r="Y29" s="1" t="s">
-        <v>61</v>
+        <v>58</v>
       </c>
       <c r="Z29" s="1" t="s">
-        <v>87</v>
+        <v>83</v>
       </c>
       <c r="AA29" t="s">
-        <v>100</v>
+        <v>96</v>
       </c>
     </row>
     <row r="30" spans="1:27">
@@ -2382,7 +2383,7 @@
         <v>309</v>
       </c>
       <c r="B30" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="C30">
         <v>8</v>
@@ -2409,13 +2410,13 @@
         <v>300</v>
       </c>
       <c r="K30" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="L30">
         <v>50</v>
       </c>
       <c r="M30" t="s">
-        <v>78</v>
+        <v>74</v>
       </c>
       <c r="N30">
         <v>40</v>
@@ -2424,7 +2425,7 @@
         <v>40</v>
       </c>
       <c r="P30" t="s">
-        <v>79</v>
+        <v>75</v>
       </c>
       <c r="Q30">
         <v>10</v>
@@ -2433,7 +2434,7 @@
         <v>10</v>
       </c>
       <c r="S30" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="T30">
         <v>30</v>
@@ -2442,7 +2443,7 @@
         <v>30</v>
       </c>
       <c r="V30" t="s">
-        <v>83</v>
+        <v>79</v>
       </c>
       <c r="W30">
         <v>5</v>
@@ -2451,13 +2452,13 @@
         <v>10</v>
       </c>
       <c r="Y30" s="1" t="s">
-        <v>62</v>
+        <v>59</v>
       </c>
       <c r="Z30" s="1" t="s">
-        <v>87</v>
+        <v>83</v>
       </c>
       <c r="AA30" t="s">
-        <v>100</v>
+        <v>96</v>
       </c>
     </row>
     <row r="31" spans="1:27">
@@ -2465,13 +2466,13 @@
         <v>310</v>
       </c>
       <c r="B31" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="C31">
         <v>9</v>
       </c>
       <c r="M31" t="s">
-        <v>78</v>
+        <v>74</v>
       </c>
       <c r="N31">
         <v>50</v>
@@ -2480,7 +2481,7 @@
         <v>50</v>
       </c>
       <c r="P31" t="s">
-        <v>79</v>
+        <v>75</v>
       </c>
       <c r="Q31">
         <v>15</v>
@@ -2489,7 +2490,7 @@
         <v>15</v>
       </c>
       <c r="S31" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="T31">
         <v>50</v>
@@ -2498,7 +2499,7 @@
         <v>50</v>
       </c>
       <c r="V31" t="s">
-        <v>83</v>
+        <v>79</v>
       </c>
       <c r="W31">
         <v>10</v>
@@ -2507,13 +2508,13 @@
         <v>15</v>
       </c>
       <c r="Y31" s="1" t="s">
-        <v>63</v>
+        <v>60</v>
       </c>
       <c r="Z31" s="1" t="s">
-        <v>87</v>
+        <v>83</v>
       </c>
       <c r="AA31" t="s">
-        <v>101</v>
+        <v>97</v>
       </c>
     </row>
     <row r="32" spans="1:27">
@@ -2521,7 +2522,7 @@
         <v>401</v>
       </c>
       <c r="B32" t="s">
-        <v>64</v>
+        <v>61</v>
       </c>
       <c r="C32">
         <v>0</v>
@@ -2548,13 +2549,13 @@
         <v>10</v>
       </c>
       <c r="Y32" s="1" t="s">
-        <v>65</v>
+        <v>106</v>
       </c>
       <c r="Z32" s="1" t="s">
+        <v>84</v>
+      </c>
+      <c r="AA32" t="s">
         <v>88</v>
-      </c>
-      <c r="AA32" t="s">
-        <v>92</v>
       </c>
     </row>
     <row r="33" spans="1:27">
@@ -2562,7 +2563,7 @@
         <v>402</v>
       </c>
       <c r="B33" t="s">
-        <v>64</v>
+        <v>61</v>
       </c>
       <c r="C33">
         <v>1</v>
@@ -2589,7 +2590,7 @@
         <v>25</v>
       </c>
       <c r="M33" t="s">
-        <v>90</v>
+        <v>86</v>
       </c>
       <c r="N33">
         <v>5</v>
@@ -2598,7 +2599,7 @@
         <v>5</v>
       </c>
       <c r="P33" t="s">
-        <v>105</v>
+        <v>101</v>
       </c>
       <c r="Q33">
         <v>1</v>
@@ -2607,13 +2608,13 @@
         <v>1</v>
       </c>
       <c r="Y33" s="1" t="s">
-        <v>66</v>
+        <v>62</v>
       </c>
       <c r="Z33" s="1" t="s">
-        <v>88</v>
+        <v>84</v>
       </c>
       <c r="AA33" t="s">
-        <v>102</v>
+        <v>98</v>
       </c>
     </row>
     <row r="34" spans="1:27">
@@ -2621,7 +2622,7 @@
         <v>403</v>
       </c>
       <c r="B34" t="s">
-        <v>64</v>
+        <v>61</v>
       </c>
       <c r="C34">
         <v>2</v>
@@ -2648,7 +2649,7 @@
         <v>60</v>
       </c>
       <c r="M34" t="s">
-        <v>90</v>
+        <v>86</v>
       </c>
       <c r="N34">
         <v>5</v>
@@ -2657,7 +2658,7 @@
         <v>5</v>
       </c>
       <c r="P34" t="s">
-        <v>105</v>
+        <v>101</v>
       </c>
       <c r="Q34">
         <v>1</v>
@@ -2666,13 +2667,13 @@
         <v>1</v>
       </c>
       <c r="Y34" s="1" t="s">
-        <v>67</v>
+        <v>63</v>
       </c>
       <c r="Z34" s="1" t="s">
-        <v>88</v>
+        <v>84</v>
       </c>
       <c r="AA34" t="s">
-        <v>102</v>
+        <v>98</v>
       </c>
     </row>
     <row r="35" spans="1:27">
@@ -2680,7 +2681,7 @@
         <v>404</v>
       </c>
       <c r="B35" t="s">
-        <v>64</v>
+        <v>61</v>
       </c>
       <c r="C35">
         <v>3</v>
@@ -2707,7 +2708,7 @@
         <v>100</v>
       </c>
       <c r="M35" t="s">
-        <v>90</v>
+        <v>86</v>
       </c>
       <c r="N35">
         <v>7.5</v>
@@ -2716,7 +2717,7 @@
         <v>7.5</v>
       </c>
       <c r="P35" t="s">
-        <v>81</v>
+        <v>77</v>
       </c>
       <c r="Q35">
         <v>2</v>
@@ -2725,13 +2726,13 @@
         <v>2</v>
       </c>
       <c r="Y35" s="1" t="s">
-        <v>68</v>
+        <v>64</v>
       </c>
       <c r="Z35" s="1" t="s">
-        <v>88</v>
+        <v>84</v>
       </c>
       <c r="AA35" t="s">
-        <v>102</v>
+        <v>98</v>
       </c>
     </row>
     <row r="36" spans="1:27">
@@ -2739,7 +2740,7 @@
         <v>405</v>
       </c>
       <c r="B36" t="s">
-        <v>64</v>
+        <v>61</v>
       </c>
       <c r="C36">
         <v>4</v>
@@ -2766,13 +2767,13 @@
         <v>150</v>
       </c>
       <c r="K36" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="L36">
         <v>1</v>
       </c>
       <c r="M36" t="s">
-        <v>90</v>
+        <v>86</v>
       </c>
       <c r="N36">
         <v>7.5</v>
@@ -2781,7 +2782,7 @@
         <v>7.5</v>
       </c>
       <c r="P36" t="s">
-        <v>81</v>
+        <v>77</v>
       </c>
       <c r="Q36">
         <v>2</v>
@@ -2790,13 +2791,13 @@
         <v>2</v>
       </c>
       <c r="Y36" s="1" t="s">
-        <v>69</v>
+        <v>65</v>
       </c>
       <c r="Z36" s="1" t="s">
-        <v>88</v>
+        <v>84</v>
       </c>
       <c r="AA36" t="s">
-        <v>102</v>
+        <v>98</v>
       </c>
     </row>
     <row r="37" spans="1:27">
@@ -2804,7 +2805,7 @@
         <v>406</v>
       </c>
       <c r="B37" t="s">
-        <v>64</v>
+        <v>61</v>
       </c>
       <c r="C37">
         <v>5</v>
@@ -2831,13 +2832,13 @@
         <v>225</v>
       </c>
       <c r="K37" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="L37">
         <v>15</v>
       </c>
       <c r="M37" t="s">
-        <v>90</v>
+        <v>86</v>
       </c>
       <c r="N37">
         <v>7.5</v>
@@ -2846,7 +2847,7 @@
         <v>7.5</v>
       </c>
       <c r="P37" t="s">
-        <v>81</v>
+        <v>77</v>
       </c>
       <c r="Q37">
         <v>2</v>
@@ -2855,13 +2856,13 @@
         <v>2</v>
       </c>
       <c r="Y37" s="1" t="s">
-        <v>70</v>
+        <v>66</v>
       </c>
       <c r="Z37" s="1" t="s">
-        <v>88</v>
+        <v>84</v>
       </c>
       <c r="AA37" t="s">
-        <v>103</v>
+        <v>99</v>
       </c>
     </row>
     <row r="38" spans="1:27">
@@ -2869,7 +2870,7 @@
         <v>407</v>
       </c>
       <c r="B38" t="s">
-        <v>64</v>
+        <v>61</v>
       </c>
       <c r="C38">
         <v>6</v>
@@ -2896,13 +2897,13 @@
         <v>300</v>
       </c>
       <c r="K38" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="L38">
         <v>35</v>
       </c>
       <c r="M38" t="s">
-        <v>90</v>
+        <v>86</v>
       </c>
       <c r="N38">
         <v>10</v>
@@ -2911,7 +2912,7 @@
         <v>10</v>
       </c>
       <c r="P38" t="s">
-        <v>81</v>
+        <v>77</v>
       </c>
       <c r="Q38">
         <v>4</v>
@@ -2920,7 +2921,7 @@
         <v>4</v>
       </c>
       <c r="S38" t="s">
-        <v>106</v>
+        <v>102</v>
       </c>
       <c r="T38">
         <v>1</v>
@@ -2929,13 +2930,13 @@
         <v>1</v>
       </c>
       <c r="Y38" s="1" t="s">
-        <v>71</v>
+        <v>67</v>
       </c>
       <c r="Z38" s="1" t="s">
-        <v>88</v>
+        <v>84</v>
       </c>
       <c r="AA38" t="s">
-        <v>103</v>
+        <v>99</v>
       </c>
     </row>
     <row r="39" spans="1:27">
@@ -2943,7 +2944,7 @@
         <v>408</v>
       </c>
       <c r="B39" t="s">
-        <v>64</v>
+        <v>61</v>
       </c>
       <c r="C39">
         <v>7</v>
@@ -2970,13 +2971,13 @@
         <v>400</v>
       </c>
       <c r="K39" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="L39">
         <v>70</v>
       </c>
       <c r="M39" t="s">
-        <v>90</v>
+        <v>86</v>
       </c>
       <c r="N39">
         <v>10</v>
@@ -2985,7 +2986,7 @@
         <v>10</v>
       </c>
       <c r="P39" t="s">
-        <v>81</v>
+        <v>77</v>
       </c>
       <c r="Q39">
         <v>4</v>
@@ -2994,7 +2995,7 @@
         <v>4</v>
       </c>
       <c r="S39" t="s">
-        <v>106</v>
+        <v>102</v>
       </c>
       <c r="T39">
         <v>1</v>
@@ -3003,13 +3004,13 @@
         <v>1</v>
       </c>
       <c r="Y39" s="1" t="s">
-        <v>72</v>
+        <v>68</v>
       </c>
       <c r="Z39" s="1" t="s">
-        <v>88</v>
+        <v>84</v>
       </c>
       <c r="AA39" t="s">
-        <v>103</v>
+        <v>99</v>
       </c>
     </row>
     <row r="40" spans="1:27">
@@ -3017,7 +3018,7 @@
         <v>409</v>
       </c>
       <c r="B40" t="s">
-        <v>64</v>
+        <v>61</v>
       </c>
       <c r="C40">
         <v>8</v>
@@ -3044,13 +3045,13 @@
         <v>500</v>
       </c>
       <c r="K40" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="L40">
         <v>120</v>
       </c>
       <c r="M40" t="s">
-        <v>90</v>
+        <v>86</v>
       </c>
       <c r="N40">
         <v>10</v>
@@ -3059,7 +3060,7 @@
         <v>10</v>
       </c>
       <c r="P40" t="s">
-        <v>81</v>
+        <v>77</v>
       </c>
       <c r="Q40">
         <v>4</v>
@@ -3068,7 +3069,7 @@
         <v>4</v>
       </c>
       <c r="S40" t="s">
-        <v>106</v>
+        <v>102</v>
       </c>
       <c r="T40">
         <v>1</v>
@@ -3077,13 +3078,13 @@
         <v>1</v>
       </c>
       <c r="Y40" s="1" t="s">
-        <v>73</v>
+        <v>69</v>
       </c>
       <c r="Z40" s="1" t="s">
-        <v>88</v>
+        <v>84</v>
       </c>
       <c r="AA40" t="s">
-        <v>103</v>
+        <v>99</v>
       </c>
     </row>
     <row r="41" spans="1:27">
@@ -3091,13 +3092,13 @@
         <v>410</v>
       </c>
       <c r="B41" t="s">
-        <v>64</v>
+        <v>61</v>
       </c>
       <c r="C41">
         <v>9</v>
       </c>
       <c r="M41" t="s">
-        <v>90</v>
+        <v>86</v>
       </c>
       <c r="N41">
         <v>12.5</v>
@@ -3106,7 +3107,7 @@
         <v>12.5</v>
       </c>
       <c r="P41" t="s">
-        <v>81</v>
+        <v>77</v>
       </c>
       <c r="Q41">
         <v>6</v>
@@ -3115,7 +3116,7 @@
         <v>6</v>
       </c>
       <c r="S41" t="s">
-        <v>82</v>
+        <v>78</v>
       </c>
       <c r="T41">
         <v>2</v>
@@ -3124,13 +3125,13 @@
         <v>2</v>
       </c>
       <c r="Y41" s="1" t="s">
-        <v>74</v>
+        <v>70</v>
       </c>
       <c r="Z41" s="1" t="s">
-        <v>88</v>
+        <v>84</v>
       </c>
       <c r="AA41" t="s">
-        <v>104</v>
+        <v>100</v>
       </c>
     </row>
   </sheetData>

--- a/Assets/Excel/BuildingUpgradeSO.xlsx
+++ b/Assets/Excel/BuildingUpgradeSO.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29127"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29231"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Users\User\TeamProject_CheerUpMyHero\Assets\Excel\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\USER\Documents\GitHub\TeamProject_CheerUpMyHero\Assets\Excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9654631B-3D35-4B1E-9D8D-0DD3E23E6A41}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{86F00300-4226-41A4-AF0E-8E8B74E0E413}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1275" yWindow="-120" windowWidth="27645" windowHeight="16440" xr2:uid="{529EFE37-1A1C-40A3-AFC4-E608165EEB57}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{529EFE37-1A1C-40A3-AFC4-E608165EEB57}"/>
   </bookViews>
   <sheets>
     <sheet name="BuildingUpgrade" sheetId="1" r:id="rId1"/>
@@ -940,10 +940,10 @@
         <v>80</v>
       </c>
       <c r="N3">
-        <v>500</v>
+        <v>1000</v>
       </c>
       <c r="O3">
-        <v>500</v>
+        <v>1000</v>
       </c>
       <c r="P3" t="s">
         <v>71</v>
@@ -987,10 +987,10 @@
         <v>80</v>
       </c>
       <c r="N4">
-        <v>750</v>
+        <v>1500</v>
       </c>
       <c r="O4">
-        <v>750</v>
+        <v>1500</v>
       </c>
       <c r="P4" t="s">
         <v>71</v>
@@ -1040,10 +1040,10 @@
         <v>80</v>
       </c>
       <c r="N5">
-        <v>1000</v>
+        <v>2000</v>
       </c>
       <c r="O5">
-        <v>1000</v>
+        <v>2000</v>
       </c>
       <c r="P5" t="s">
         <v>71</v>
@@ -1099,10 +1099,10 @@
         <v>80</v>
       </c>
       <c r="N6">
-        <v>1250</v>
+        <v>2500</v>
       </c>
       <c r="O6">
-        <v>1250</v>
+        <v>2500</v>
       </c>
       <c r="P6" t="s">
         <v>71</v>
@@ -1158,10 +1158,10 @@
         <v>80</v>
       </c>
       <c r="N7">
-        <v>1500</v>
+        <v>3000</v>
       </c>
       <c r="O7">
-        <v>1500</v>
+        <v>3000</v>
       </c>
       <c r="P7" t="s">
         <v>71</v>
@@ -1217,10 +1217,10 @@
         <v>80</v>
       </c>
       <c r="N8">
-        <v>1750</v>
+        <v>3500</v>
       </c>
       <c r="O8">
-        <v>1750</v>
+        <v>3500</v>
       </c>
       <c r="P8" t="s">
         <v>71</v>
@@ -1276,10 +1276,10 @@
         <v>80</v>
       </c>
       <c r="N9">
-        <v>2000</v>
+        <v>4000</v>
       </c>
       <c r="O9">
-        <v>2000</v>
+        <v>4000</v>
       </c>
       <c r="P9" t="s">
         <v>71</v>
@@ -1335,10 +1335,10 @@
         <v>80</v>
       </c>
       <c r="N10">
-        <v>2250</v>
+        <v>4500</v>
       </c>
       <c r="O10">
-        <v>2250</v>
+        <v>4500</v>
       </c>
       <c r="P10" t="s">
         <v>71</v>
@@ -1373,10 +1373,10 @@
         <v>80</v>
       </c>
       <c r="N11">
-        <v>2500</v>
+        <v>5000</v>
       </c>
       <c r="O11">
-        <v>2500</v>
+        <v>5000</v>
       </c>
       <c r="P11" t="s">
         <v>71</v>

--- a/Assets/Excel/BuildingUpgradeSO.xlsx
+++ b/Assets/Excel/BuildingUpgradeSO.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\USER\Documents\GitHub\TeamProject_CheerUpMyHero\Assets\Excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{86F00300-4226-41A4-AF0E-8E8B74E0E413}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BA8150EE-2171-412B-8CA7-A3DA20C679BF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{529EFE37-1A1C-40A3-AFC4-E608165EEB57}"/>
+    <workbookView xWindow="19095" yWindow="0" windowWidth="19410" windowHeight="20985" xr2:uid="{529EFE37-1A1C-40A3-AFC4-E608165EEB57}"/>
   </bookViews>
   <sheets>
     <sheet name="BuildingUpgrade" sheetId="1" r:id="rId1"/>
@@ -1099,10 +1099,10 @@
         <v>80</v>
       </c>
       <c r="N6">
-        <v>2500</v>
+        <v>3000</v>
       </c>
       <c r="O6">
-        <v>2500</v>
+        <v>3000</v>
       </c>
       <c r="P6" t="s">
         <v>71</v>
@@ -1158,10 +1158,10 @@
         <v>80</v>
       </c>
       <c r="N7">
-        <v>3000</v>
+        <v>5000</v>
       </c>
       <c r="O7">
-        <v>3000</v>
+        <v>5000</v>
       </c>
       <c r="P7" t="s">
         <v>71</v>
@@ -1217,10 +1217,10 @@
         <v>80</v>
       </c>
       <c r="N8">
-        <v>3500</v>
+        <v>6750</v>
       </c>
       <c r="O8">
-        <v>3500</v>
+        <v>6750</v>
       </c>
       <c r="P8" t="s">
         <v>71</v>
@@ -1276,10 +1276,10 @@
         <v>80</v>
       </c>
       <c r="N9">
-        <v>4000</v>
+        <v>8500</v>
       </c>
       <c r="O9">
-        <v>4000</v>
+        <v>8500</v>
       </c>
       <c r="P9" t="s">
         <v>71</v>
@@ -1335,10 +1335,10 @@
         <v>80</v>
       </c>
       <c r="N10">
-        <v>4500</v>
+        <v>10000</v>
       </c>
       <c r="O10">
-        <v>4500</v>
+        <v>10000</v>
       </c>
       <c r="P10" t="s">
         <v>71</v>
@@ -1373,10 +1373,10 @@
         <v>80</v>
       </c>
       <c r="N11">
-        <v>5000</v>
+        <v>12500</v>
       </c>
       <c r="O11">
-        <v>5000</v>
+        <v>12500</v>
       </c>
       <c r="P11" t="s">
         <v>71</v>

--- a/Assets/Excel/BuildingUpgradeSO.xlsx
+++ b/Assets/Excel/BuildingUpgradeSO.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\USER\Documents\GitHub\TeamProject_CheerUpMyHero\Assets\Excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BA8150EE-2171-412B-8CA7-A3DA20C679BF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C54E7405-4FE7-4510-AEFF-8D9A2ECDB785}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="19095" yWindow="0" windowWidth="19410" windowHeight="20985" xr2:uid="{529EFE37-1A1C-40A3-AFC4-E608165EEB57}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{529EFE37-1A1C-40A3-AFC4-E608165EEB57}"/>
   </bookViews>
   <sheets>
     <sheet name="BuildingUpgrade" sheetId="1" r:id="rId1"/>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="370" uniqueCount="107">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="371" uniqueCount="107">
   <si>
     <t>idNumber</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -2855,6 +2855,15 @@
       <c r="R37">
         <v>2</v>
       </c>
+      <c r="S37" t="s">
+        <v>102</v>
+      </c>
+      <c r="T37">
+        <v>1</v>
+      </c>
+      <c r="U37">
+        <v>1</v>
+      </c>
       <c r="Y37" s="1" t="s">
         <v>66</v>
       </c>

--- a/Assets/Excel/BuildingUpgradeSO.xlsx
+++ b/Assets/Excel/BuildingUpgradeSO.xlsx
@@ -1,21 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29231"/>
-  <workbookPr defaultThemeVersion="166925"/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\USER\Documents\GitHub\TeamProject_CheerUpMyHero\Assets\Excel\"/>
-    </mc:Choice>
-  </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C54E7405-4FE7-4510-AEFF-8D9A2ECDB785}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <fileVersion appName="xl" lastEdited="5" lowestEdited="7" rupBuild="9302"/>
+  <workbookPr/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{529EFE37-1A1C-40A3-AFC4-E608165EEB57}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="16440"/>
   </bookViews>
   <sheets>
     <sheet name="BuildingUpgrade" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="191029"/>
+  <calcPr calcId="144525"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -393,27 +387,27 @@
     <t>CanSummonEpicUnits</t>
   </si>
   <si>
-    <t>안정적으로 식량을 확보합니다.</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>안정적으로 목재를 확보합니다.</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>안정적으로 철괴를 확보합니다.</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>전투에 투입할 수 있는 유닛의 쿨타임을 감소시킵니다.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>스테이지 클리어 시 목재를 확보합니다.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>스테이지 클리어 시 철괴를 확보합니다.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>스테이지에 사용 될 식량을 확보합니다.</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="5">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <fonts count="5" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -548,7 +542,7 @@
     </a:clrScheme>
     <a:fontScheme name="Office">
       <a:majorFont>
-        <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
+        <a:latin typeface="Calibri Light"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="游ゴシック Light"/>
@@ -600,7 +594,7 @@
         <a:font script="Tfng" typeface="Ebrima"/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="Calibri" panose="020F0502020204030204"/>
+        <a:latin typeface="Calibri"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="游ゴシック"/>
@@ -794,18 +788,18 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" xmlns="" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{51A90E86-42B4-4D3F-9CF6-60D01B3BDC85}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:AA41"/>
-  <sheetFormatPr defaultRowHeight="16.5"/>
+  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <sheetData>
-    <row r="1" spans="1:27">
+    <row r="1" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -888,7 +882,7 @@
         <v>87</v>
       </c>
     </row>
-    <row r="2" spans="1:27">
+    <row r="2" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A2">
         <v>101</v>
       </c>
@@ -908,7 +902,7 @@
         <v>100</v>
       </c>
       <c r="Y2" s="1" t="s">
-        <v>103</v>
+        <v>106</v>
       </c>
       <c r="Z2" s="1" t="s">
         <v>81</v>
@@ -917,7 +911,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="3" spans="1:27">
+    <row r="3" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A3">
         <v>102</v>
       </c>
@@ -964,7 +958,7 @@
         <v>89</v>
       </c>
     </row>
-    <row r="4" spans="1:27">
+    <row r="4" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A4">
         <v>103</v>
       </c>
@@ -1011,7 +1005,7 @@
         <v>89</v>
       </c>
     </row>
-    <row r="5" spans="1:27">
+    <row r="5" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A5">
         <v>104</v>
       </c>
@@ -1064,7 +1058,7 @@
         <v>89</v>
       </c>
     </row>
-    <row r="6" spans="1:27">
+    <row r="6" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A6">
         <v>105</v>
       </c>
@@ -1123,7 +1117,7 @@
         <v>89</v>
       </c>
     </row>
-    <row r="7" spans="1:27">
+    <row r="7" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A7">
         <v>106</v>
       </c>
@@ -1182,7 +1176,7 @@
         <v>91</v>
       </c>
     </row>
-    <row r="8" spans="1:27">
+    <row r="8" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A8">
         <v>107</v>
       </c>
@@ -1241,7 +1235,7 @@
         <v>91</v>
       </c>
     </row>
-    <row r="9" spans="1:27">
+    <row r="9" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A9">
         <v>108</v>
       </c>
@@ -1300,7 +1294,7 @@
         <v>91</v>
       </c>
     </row>
-    <row r="10" spans="1:27">
+    <row r="10" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A10">
         <v>109</v>
       </c>
@@ -1359,7 +1353,7 @@
         <v>91</v>
       </c>
     </row>
-    <row r="11" spans="1:27">
+    <row r="11" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A11">
         <v>110</v>
       </c>
@@ -1397,7 +1391,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="12" spans="1:27">
+    <row r="12" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A12">
         <v>201</v>
       </c>
@@ -1426,7 +1420,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="13" spans="1:27">
+    <row r="13" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A13">
         <v>202</v>
       </c>
@@ -1464,7 +1458,7 @@
         <v>92</v>
       </c>
     </row>
-    <row r="14" spans="1:27">
+    <row r="14" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A14">
         <v>203</v>
       </c>
@@ -1508,7 +1502,7 @@
         <v>92</v>
       </c>
     </row>
-    <row r="15" spans="1:27">
+    <row r="15" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A15">
         <v>204</v>
       </c>
@@ -1567,7 +1561,7 @@
         <v>92</v>
       </c>
     </row>
-    <row r="16" spans="1:27">
+    <row r="16" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A16">
         <v>205</v>
       </c>
@@ -1626,7 +1620,7 @@
         <v>92</v>
       </c>
     </row>
-    <row r="17" spans="1:27">
+    <row r="17" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A17">
         <v>206</v>
       </c>
@@ -1685,7 +1679,7 @@
         <v>93</v>
       </c>
     </row>
-    <row r="18" spans="1:27">
+    <row r="18" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A18">
         <v>207</v>
       </c>
@@ -1744,7 +1738,7 @@
         <v>93</v>
       </c>
     </row>
-    <row r="19" spans="1:27">
+    <row r="19" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A19">
         <v>208</v>
       </c>
@@ -1803,7 +1797,7 @@
         <v>93</v>
       </c>
     </row>
-    <row r="20" spans="1:27">
+    <row r="20" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A20">
         <v>209</v>
       </c>
@@ -1862,7 +1856,7 @@
         <v>93</v>
       </c>
     </row>
-    <row r="21" spans="1:27">
+    <row r="21" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A21">
         <v>210</v>
       </c>
@@ -1900,7 +1894,7 @@
         <v>94</v>
       </c>
     </row>
-    <row r="22" spans="1:27">
+    <row r="22" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A22">
         <v>301</v>
       </c>
@@ -1935,7 +1929,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="23" spans="1:27">
+    <row r="23" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A23">
         <v>302</v>
       </c>
@@ -1979,7 +1973,7 @@
         <v>95</v>
       </c>
     </row>
-    <row r="24" spans="1:27">
+    <row r="24" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A24">
         <v>303</v>
       </c>
@@ -2029,7 +2023,7 @@
         <v>95</v>
       </c>
     </row>
-    <row r="25" spans="1:27">
+    <row r="25" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A25">
         <v>304</v>
       </c>
@@ -2088,7 +2082,7 @@
         <v>95</v>
       </c>
     </row>
-    <row r="26" spans="1:27">
+    <row r="26" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A26">
         <v>305</v>
       </c>
@@ -2147,7 +2141,7 @@
         <v>95</v>
       </c>
     </row>
-    <row r="27" spans="1:27">
+    <row r="27" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A27">
         <v>306</v>
       </c>
@@ -2212,7 +2206,7 @@
         <v>96</v>
       </c>
     </row>
-    <row r="28" spans="1:27">
+    <row r="28" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A28">
         <v>307</v>
       </c>
@@ -2295,7 +2289,7 @@
         <v>96</v>
       </c>
     </row>
-    <row r="29" spans="1:27">
+    <row r="29" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A29">
         <v>308</v>
       </c>
@@ -2378,7 +2372,7 @@
         <v>96</v>
       </c>
     </row>
-    <row r="30" spans="1:27">
+    <row r="30" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A30">
         <v>309</v>
       </c>
@@ -2461,7 +2455,7 @@
         <v>96</v>
       </c>
     </row>
-    <row r="31" spans="1:27">
+    <row r="31" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A31">
         <v>310</v>
       </c>
@@ -2517,7 +2511,7 @@
         <v>97</v>
       </c>
     </row>
-    <row r="32" spans="1:27">
+    <row r="32" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A32">
         <v>401</v>
       </c>
@@ -2549,7 +2543,7 @@
         <v>10</v>
       </c>
       <c r="Y32" s="1" t="s">
-        <v>106</v>
+        <v>103</v>
       </c>
       <c r="Z32" s="1" t="s">
         <v>84</v>
@@ -2558,7 +2552,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="33" spans="1:27">
+    <row r="33" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A33">
         <v>402</v>
       </c>
@@ -2617,7 +2611,7 @@
         <v>98</v>
       </c>
     </row>
-    <row r="34" spans="1:27">
+    <row r="34" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A34">
         <v>403</v>
       </c>
@@ -2676,7 +2670,7 @@
         <v>98</v>
       </c>
     </row>
-    <row r="35" spans="1:27">
+    <row r="35" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A35">
         <v>404</v>
       </c>
@@ -2735,7 +2729,7 @@
         <v>98</v>
       </c>
     </row>
-    <row r="36" spans="1:27">
+    <row r="36" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A36">
         <v>405</v>
       </c>
@@ -2800,7 +2794,7 @@
         <v>98</v>
       </c>
     </row>
-    <row r="37" spans="1:27">
+    <row r="37" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A37">
         <v>406</v>
       </c>
@@ -2874,7 +2868,7 @@
         <v>99</v>
       </c>
     </row>
-    <row r="38" spans="1:27">
+    <row r="38" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A38">
         <v>407</v>
       </c>
@@ -2948,7 +2942,7 @@
         <v>99</v>
       </c>
     </row>
-    <row r="39" spans="1:27">
+    <row r="39" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A39">
         <v>408</v>
       </c>
@@ -3022,7 +3016,7 @@
         <v>99</v>
       </c>
     </row>
-    <row r="40" spans="1:27">
+    <row r="40" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A40">
         <v>409</v>
       </c>
@@ -3096,7 +3090,7 @@
         <v>99</v>
       </c>
     </row>
-    <row r="41" spans="1:27">
+    <row r="41" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A41">
         <v>410</v>
       </c>
